--- a/results/Int Task Remove ACC -0.0/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_4_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8214822266181121</v>
+        <v>0.8100844460429499</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8312146892655368</v>
+        <v>0.8100844460429499</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8282306043849001</v>
+        <v>0.8050894288839935</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8465790735662155</v>
+        <v>0.8071949602122016</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8392584183788159</v>
+        <v>0.7964556264892326</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8392584183788159</v>
+        <v>0.8023160844610289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8404469945600863</v>
+        <v>0.802626107089871</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8511001588514738</v>
+        <v>0.8047016664418769</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.846018972260936</v>
+        <v>0.8099851638717799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8089267784621379</v>
+        <v>0.7845408293245815</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7942517496141108</v>
+        <v>0.7845408293245815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8091684275202685</v>
+        <v>0.7848723943113189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.812160942019212</v>
+        <v>0.7848723943113189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.812888699066373</v>
+        <v>0.7821421346041452</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8041387552638284</v>
+        <v>0.7892773381887934</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8034109982166675</v>
+        <v>0.7924768466483838</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8061496875421481</v>
+        <v>0.7746622532931708</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8064512805526832</v>
+        <v>0.7469400485546014</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8061197155659459</v>
+        <v>0.7136290068785686</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.794115002472688</v>
+        <v>0.7141759954442597</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7980937823135368</v>
+        <v>0.7121435208080444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8000616298760659</v>
+        <v>0.7136205772602616</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.813216517556085</v>
+        <v>0.7263586671462183</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8110763311303931</v>
+        <v>0.7273533621064305</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7178981402388767</v>
+        <v>0.7283911417824334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7131138635375924</v>
+        <v>0.7210105426426292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7264326604624676</v>
+        <v>0.728495107074885</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7219153216742346</v>
+        <v>0.7238485141392799</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6706257773981328</v>
+        <v>0.7101466378935695</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6369054309220878</v>
+        <v>0.686970807295179</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6331551873997812</v>
+        <v>0.6757921967959958</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6320012663159945</v>
+        <v>0.6927975467937478</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6376247583509418</v>
+        <v>0.6993557898365028</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6333574982391464</v>
+        <v>0.6877847337739214</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6274923571460684</v>
+        <v>0.6877847337739214</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6356091429513404</v>
+        <v>0.694941479716465</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6280215498508894</v>
+        <v>0.6807057276446522</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5810432870266301</v>
+        <v>0.6604268758710605</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5800485920664179</v>
+        <v>0.5590934975797629</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5799839649927317</v>
+        <v>0.5883096180071633</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.569438512490821</v>
+        <v>0.6024807430052901</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5782736891006909</v>
+        <v>0.6024592006473947</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.544798738179802</v>
+        <v>0.5675446582445414</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5450656760928532</v>
+        <v>0.5536104991832637</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5233078946185317</v>
+        <v>0.5586448545609854</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5233078946185317</v>
+        <v>0.5611980922837148</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5195660807145319</v>
+        <v>0.5651384705300544</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5144165205532827</v>
+        <v>0.5622190127231039</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5223956225928756</v>
+        <v>0.5477743934421316</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.522727187579613</v>
+        <v>0.5477743934421316</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5177752551364474</v>
+        <v>0.5477743934421316</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5177752551364474</v>
+        <v>0.5427362915673846</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5012185481574728</v>
+        <v>0.5483944386998156</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5005338758261026</v>
+        <v>0.564254297232088</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5008869831707354</v>
+        <v>0.5437056976726761</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5008869831707354</v>
+        <v>0.5518917936729157</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5012185481574728</v>
+        <v>0.5793554901167408</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5016147402178963</v>
+        <v>0.6660466214089826</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5016147402178963</v>
+        <v>0.6708177853706785</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5019893899204244</v>
+        <v>0.6731733953753241</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5005985028997887</v>
+        <v>0.6149312892445563</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5006200452576841</v>
+        <v>0.6009287566125673</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5013047175890543</v>
+        <v>0.620146413103748</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5009731526023168</v>
+        <v>0.6267992551963913</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5006200452576841</v>
+        <v>0.6408842107629367</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5019463052046337</v>
+        <v>0.6588186920229585</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5046203674564282</v>
+        <v>0.662968874102714</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5049303900852703</v>
+        <v>0.6623057441292391</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5029410001648459</v>
+        <v>0.6507440543092209</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5026094351781085</v>
+        <v>0.6498870431146877</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.502277870191371</v>
+        <v>0.6498870431146877</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5019463052046337</v>
+        <v>0.6357018687527163</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5026094351781085</v>
+        <v>0.6357018687527163</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5054211811955821</v>
+        <v>0.6428970162897691</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4992291582370484</v>
+        <v>0.6423453446027964</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.499207615879153</v>
+        <v>0.6367658739078961</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4967789491825143</v>
+        <v>0.6292213655232357</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4992507005949437</v>
+        <v>0.6511308801270812</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4992507005949437</v>
+        <v>0.5600366782058775</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.495719627148616</v>
+        <v>0.5549639212336466</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4986821696713573</v>
+        <v>0.5440831572479732</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4986821696713573</v>
+        <v>0.5240609405206132</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4969166329481934</v>
+        <v>0.5211630250715581</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4969166329481934</v>
+        <v>0.5025232657465269</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4969381753060888</v>
+        <v>0.5005769605418933</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4998276611368371</v>
+        <v>0.5002669379130513</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4998276611368371</v>
+        <v>0.5002023108393652</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4966927797509329</v>
+        <v>0.4992291582370484</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4977090170690404</v>
+        <v>0.4992507005949437</v>
       </c>
     </row>
   </sheetData>
